--- a/artfynd/A 25163-2024 artfynd.xlsx
+++ b/artfynd/A 25163-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107675277</v>
+        <v>111616248</v>
       </c>
       <c r="B3" t="n">
-        <v>102161</v>
+        <v>102184</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>vägkors svederna, Ög</t>
+          <t>Svartmålen, 85 m NV norra vägskälet, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537815.8133477407</v>
+        <v>537839.360313203</v>
       </c>
       <c r="R3" t="n">
-        <v>6437783.331988758</v>
+        <v>6437758.700135854</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,14 +880,9 @@
           <t>Västra Eneby</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>E-Kin-0677</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-07-04</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -897,7 +892,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-07-04</t>
+          <t>2023-08-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -907,7 +902,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Växer i korsningen till lokal benämnd svederna, på båda sidor av vägen. Medobservatör: Leif Andersson</t>
+          <t>ny lokal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,283 +914,23 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>skogsvägkant</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Monika Sunhede</t>
+          <t>Anders Svenson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>111616248</v>
-      </c>
-      <c r="B4" t="n">
-        <v>102184</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1560</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spindelört</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Thesium alpinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Svartmålen, 85 m NV norra vägskälet, Ög</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>537839.360313203</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6437758.700135854</v>
-      </c>
-      <c r="S4" t="n">
-        <v>5</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Kinda</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Västra Eneby</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ny lokal</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>skogsvägkant</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Anders Svenson, Tommy Nilsson</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>113349489</v>
-      </c>
-      <c r="B5" t="n">
-        <v>103629</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1560</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Spindelört</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Thesium alpinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Svartmålen, 85 m NV norra vägskälet, Ög</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>537839</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6437759</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Kinda</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Västra Eneby</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>E-Kin-0691</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ny lokal</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>skogsvägkant</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Monika Sunhede</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anders Svenson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
